--- a/files/Audited_Financials.xlsx
+++ b/files/Audited_Financials.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Findings Register" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,26 +26,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
-      <sz val="14"/>
+      <sz val="16"/>
     </font>
     <font>
-      <i val="1"/>
-      <color rgb="006B7280"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-    </font>
-    <font>
+      <name val="Calibri"/>
       <i val="1"/>
       <color rgb="006B7280"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00222222"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -55,10 +59,17 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F2D55"/>
+        <bgColor rgb="001F2D55"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4F6FB"/>
+        <bgColor rgb="00F4F6FB"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -66,22 +77,47 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D7E2"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D7E2"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D7E2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D7E2"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+      <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -447,17 +483,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="50" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Audited Financials</t>
@@ -467,111 +507,601 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Audited_Financials.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
+          <t>Source file: Audited_Financials.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Ref</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>Severity</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>FY2026 Plan</t>
+          <t>Domain</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>Raised</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Target Close</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>% Complete</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Revenue (RM m)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1850</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2020</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2210</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>CAGR ~9%</t>
-        </is>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>F-2026-001</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Segregation of duties — vendor master maintenance</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Hadar Caspit</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>EBITDA (RM m)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>412</v>
-      </c>
-      <c r="C6" t="n">
-        <v>455</v>
-      </c>
-      <c r="D6" t="n">
-        <v>510</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Margin lift</t>
-        </is>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>F-2026-002</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Privileged access review lapsed at SHM division</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="G6" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H6" s="6" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Net Margin (%)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="C7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="D7" t="n">
-        <v>13</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Above peer median</t>
-        </is>
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>F-2026-003</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Three-way-match override — single remote site</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Sasha Ouellet</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-02</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>F-2026-004</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Quarterly counter-cash count inconsistency</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>Treasury</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Hadar Caspit</t>
+        </is>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="G8" s="6" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Note: placeholder demo data — not real Zava figures.</t>
-        </is>
+          <t>F-2026-005</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>KYC refresh overdue on 17 vendor accounts</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>Sasha Ouellet</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-21</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="n">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>F-2026-006</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>HSE training records incomplete at 2 sites</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>HSE</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-01</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>F-2026-007</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Stock count variance &gt;3% at central warehouse</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Operations</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>Sasha Ouellet</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>F-2026-008</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Capex approval workflow bypass — 1 instance</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>Hadar Caspit</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>F-2026-009</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Email retention policy not enforced — 2 mailboxes</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>F-2026-010</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Travel-and-expense receipts missing — 3 staff</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>Finance</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>Sasha Ouellet</t>
+        </is>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>2026-01-24</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H14" s="6" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>F-2026-011</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Software licence count below installed</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>Mod Admin</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>In progress</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>F-2026-012</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Insurance certificate expired — 1 vendor</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>Procurement</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>Sasha Ouellet</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>2026-02-28</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="H16" s="6" t="inlineStr">
+        <is>
+          <t>Closed</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
